--- a/output/pdf_financials_xlsx/WEC.xlsx
+++ b/output/pdf_financials_xlsx/WEC.xlsx
@@ -1403,16 +1403,16 @@
         <v>-52.202</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>30.328</v>
+        <v>-30.328</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>40.792</v>
+        <v>-40.792</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.534</v>
+        <v>-1.534</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>0.006</v>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-23.285116</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.631989</v>
+        <v>-15.230279</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.321</v>
+        <v>-11.638336</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.59</v>
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>11.642558</v>
+        <v>-11.642558</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>7.299145</v>
+        <v>-7.299145</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.658668</v>
+        <v>-5.658668</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-7.53046</v>
@@ -1727,16 +1727,16 @@
         <v>-52.202</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>30.328</v>
+        <v>-30.328</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>40.792</v>
+        <v>-40.792</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.534</v>
+        <v>-1.534</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.006</v>
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>11.642558</v>
+        <v>-11.642558</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>7.299145</v>
+        <v>-7.299145</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.658668</v>
+        <v>-5.658668</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-7.53046</v>
@@ -1922,16 +1922,16 @@
         <v>-52.202</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>30.328</v>
+        <v>-30.328</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>40.792</v>
+        <v>-40.792</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.534</v>
+        <v>-1.534</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.006</v>
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-68.485635</v>
+        <v>68.485635</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-72.99145</v>
+        <v>72.99145</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-80.838114</v>
+        <v>80.838114</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>188.2615</v>
@@ -2238,16 +2238,16 @@
         <v>-52.202</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>30.328</v>
+        <v>-30.328</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>40.792</v>
+        <v>-40.792</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.534</v>
+        <v>-1.534</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>0.006</v>
@@ -2368,16 +2368,16 @@
         <v>-43.679</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>35.122</v>
+        <v>-25.534</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>45.894</v>
+        <v>-35.69</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>9.273999999999999</v>
+        <v>-6.986</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.534</v>
+        <v>-1.534</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>0.006</v>
@@ -2449,13 +2449,13 @@
         <v>-122.3912799820668</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>148.175336455301</v>
+        <v>-107.7247605788297</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>139.4318699680996</v>
+        <v>-108.4308066231202</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>32.89119023975032</v>
+        <v>-24.77656405163853</v>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
@@ -2480,13 +2480,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>7.968456969709502</v>
+        <v>192.0315430302905</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>5.368191009935669</v>
+        <v>194.6318089900643</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-7.265598254286088</v>
@@ -2520,16 +2520,16 @@
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>0</v>
@@ -2601,13 +2601,13 @@
         <v>-146.2732571172383</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>127.9500485170654</v>
+        <v>-127.9500485170654</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>123.9313382956099</v>
+        <v>-123.9313382956099</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>28.83387714569443</v>
+        <v>-28.83387714569443</v>
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
@@ -67684,16 +67684,16 @@
         <v>-52.202</v>
       </c>
       <c r="Q558" s="5" t="n">
-        <v>30.328</v>
+        <v>-30.328</v>
       </c>
       <c r="R558" s="5" t="n">
-        <v>40.792</v>
+        <v>-40.792</v>
       </c>
       <c r="S558" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="T558" s="5" t="n">
-        <v>1.534</v>
+        <v>-1.534</v>
       </c>
       <c r="U558" t="inlineStr">
         <is>
@@ -67978,16 +67978,16 @@
         <v>-52.202</v>
       </c>
       <c r="Q561" s="5" t="n">
-        <v>30.328</v>
+        <v>-30.328</v>
       </c>
       <c r="R561" s="5" t="n">
-        <v>40.792</v>
+        <v>-40.792</v>
       </c>
       <c r="S561" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="T561" s="5" t="n">
-        <v>1.534</v>
+        <v>-1.534</v>
       </c>
       <c r="U561" t="inlineStr">
         <is>
@@ -85680,10 +85680,10 @@
         </is>
       </c>
       <c r="G731" s="5" t="n">
-        <v>5.658668</v>
+        <v>-5.658668</v>
       </c>
       <c r="H731" s="5" t="n">
-        <v>5.712331</v>
+        <v>-5.712331</v>
       </c>
       <c r="I731" t="inlineStr">
         <is>
@@ -87673,10 +87673,10 @@
         </is>
       </c>
       <c r="F750" s="5" t="n">
-        <v>7.299145</v>
+        <v>-7.299145</v>
       </c>
       <c r="G750" s="5" t="n">
-        <v>5.658668</v>
+        <v>-5.658668</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
@@ -89264,10 +89264,10 @@
         </is>
       </c>
       <c r="E765" s="5" t="n">
-        <v>11.642558</v>
+        <v>-11.642558</v>
       </c>
       <c r="F765" s="5" t="n">
-        <v>7.299145</v>
+        <v>-7.299145</v>
       </c>
       <c r="G765" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WEC.xlsx
+++ b/output/pdf_financials_xlsx/WEC.xlsx
@@ -978,10 +978,10 @@
         <v>2.921977</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5.815032</v>
+        <v>9.893098999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.815553</v>
+        <v>14.620442</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         <v>-2.921977</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-5.815032</v>
+        <v>-9.893098999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.815553</v>
+        <v>-14.620442</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.106409</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007938000000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.209671</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.796165</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.435962</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.338825</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2201,16 +2201,16 @@
         <v>11.642558</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7.931134</v>
+        <v>8.037542999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.979668</v>
+        <v>5.987606</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.12046</v>
+        <v>-8.330131</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>39.924555</v>
+        <v>39.12839</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-49.795602</v>
+        <v>-50.231564</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.648637</v>
+        <v>-2.987462</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-31.7</v>
@@ -2331,16 +2331,16 @@
         <v>11.642558</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.931134</v>
+        <v>8.037542999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.979668</v>
+        <v>5.987606</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.12046</v>
+        <v>-8.330131</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>39.924555</v>
+        <v>39.12839</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-49.795602</v>
+        <v>-50.231564</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.648637</v>
+        <v>-2.987462</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-31.7</v>
@@ -2687,10 +2687,10 @@
         <v>5.134</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="35">
@@ -2809,10 +2809,10 @@
         <v>5.134</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.752</v>
+        <v>1.795</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.422</v>
+        <v>1.651</v>
       </c>
     </row>
     <row r="37">
@@ -3529,16 +3529,16 @@
         <v>0.753</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.647</v>
+        <v>5.792</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.528</v>
+        <v>4.185</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.016</v>
+        <v>0.137</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.016</v>
+        <v>0.137</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -80376,7 +80376,7 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -82070,7 +82070,7 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -82286,7 +82286,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -84498,7 +84498,7 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">

--- a/output/pdf_financials_xlsx/WEC.xlsx
+++ b/output/pdf_financials_xlsx/WEC.xlsx
@@ -46348,7 +46348,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -48766,7 +48770,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
